--- a/daily-log-1.xlsx
+++ b/daily-log-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97535FCB-FD16-443D-B1AA-649F6F8148BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>Attended 4 classes, completed 3 hours of study and 1 hour of coding. Also completed 30 minutes of fitness and other activities. Overall, it was a productive day</t>
+  </si>
+  <si>
+    <t>Studied for 7 hours and completed 2 hours of coding. Also completed 30 minutes of fitness and other activities. No classes were attended today. Overall, it was a productive day</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -492,6 +498,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1082,27 +1092,51 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>420</v>
+      </c>
+      <c r="E8" s="14">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>

--- a/daily-log-1.xlsx
+++ b/daily-log-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97535FCB-FD16-443D-B1AA-649F6F8148BF}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047DA9D2-BECC-421D-838F-7BB8BD23483C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Studied for 6 hours and completed 1 hours of coding. Also completed 20 minutes of fitness and other activities. No classes were attended today. Overall, it was a productive day</t>
   </si>
 </sst>
 </file>
@@ -1138,27 +1141,49 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+    <row r="9" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>46257</v>
+      </c>
       <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="C9" s="14">
+        <v>20</v>
+      </c>
+      <c r="D9" s="14">
+        <v>360</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>940</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>

--- a/daily-log-1.xlsx
+++ b/daily-log-1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047DA9D2-BECC-421D-838F-7BB8BD23483C}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4185E42-BFB0-489A-8AD6-7CFCDF437D43}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Studied for 6 hours and completed 1 hours of coding. Also completed 20 minutes of fitness and other activities. No classes were attended today. Overall, it was a productive day</t>
+  </si>
+  <si>
+    <t>Great Day</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1148,9 @@
       <c r="A9" s="13">
         <v>46257</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
       <c r="C9" s="14">
         <v>20</v>
       </c>
@@ -1166,11 +1171,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>920</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>940</v>
+        <v>520</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>49</v>
@@ -1194,10 +1199,7 @@
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I10" s="15"/>
       <c r="J10" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1208,26 +1210,50 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>350</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
